--- a/artfynd/A 43451-2024 artfynd.xlsx
+++ b/artfynd/A 43451-2024 artfynd.xlsx
@@ -808,7 +808,7 @@
         <v>133693936</v>
       </c>
       <c r="B3" t="n">
-        <v>101389</v>
+        <v>101396</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 43451-2024 artfynd.xlsx
+++ b/artfynd/A 43451-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>105609567</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566260.2335969344</v>
+        <v>566260</v>
       </c>
       <c r="R2" t="n">
-        <v>6626735.631797221</v>
+        <v>6626735</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,19 +746,9 @@
           <t>2023-01-04</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-01-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -805,56 +790,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133693936</v>
+        <v>548997</v>
       </c>
       <c r="B3" t="n">
-        <v>101396</v>
+        <v>107270</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>1524</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Humlesuga</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Betonica officinalis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långkoxet, Ramnäs, Vstm</t>
+          <t>Tippen, Slussen, Ramnäs sn, Surahammars kn, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566503</v>
+        <v>566454</v>
       </c>
       <c r="R3" t="n">
-        <v>6626783</v>
+        <v>6626697</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -878,27 +855,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2009-06-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Enstka plantor</t>
+          <t>2009-06-29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,9 +869,13 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Ruderatmark</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -919,10 +885,484 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>89093078</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58790</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>lampa</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Roligheten, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>566153</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6626773</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2020-04-14</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2020-04-15</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Trafikverkets arbete med konfliktpunkter</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Daniel Segerlind</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Daniel Segerlind, Barbara Kühn, Tor Hansson Frank, André Dabolins</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>133693936</v>
+      </c>
+      <c r="B5" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Långkoxet, Ramnäs, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>566503</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6626783</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Enstka plantor</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
           <t>Sören Larsson, Greta Larsson</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>133694278</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99001</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Långkoxet, Ramnäs sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>566183</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6626780</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Sören Larsson, Greta Larsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6455856</v>
+      </c>
+      <c r="B7" t="n">
+        <v>103404</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>225046</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vanlig skogsalm</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Ulmus glabra subsp. glabra</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Tippen, Slussen, Ramnäs sn, Surahammars kn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>566416</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6626734</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2009-06-29</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2009-06-29</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Ruderatmark</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
